--- a/jira_export_2026-10-09.xlsx
+++ b/jira_export_2026-10-09.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>135 h</t>
+          <t>143 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P138"/>
+  <dimension ref="A1:P139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1245,7 +1245,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>3</v>
       </c>
       <c r="K32" s="15" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="L32" s="15" t="inlineStr">
         <is>
@@ -3406,27 +3406,27 @@
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34287</t>
         </is>
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t xml:space="preserve">Migration GeODP </t>
         </is>
       </c>
       <c r="F38" s="15" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G38" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H38" s="15" t="inlineStr">
@@ -3453,22 +3453,14 @@
         <v>4</v>
       </c>
       <c r="K38" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34258</t>
-        </is>
-      </c>
-      <c r="M38" s="15" t="inlineStr">
-        <is>
-          <t>00171361</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L38" s="15" t="inlineStr"/>
+      <c r="M38" s="15" t="inlineStr"/>
       <c r="N38" s="16" t="n">
-        <v>2500</v>
-      </c>
-      <c r="O38" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="16" t="n">
@@ -3478,32 +3470,32 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
@@ -3513,32 +3505,32 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>2649.6</v>
+        <v>2500</v>
       </c>
       <c r="O39" s="13" t="n">
         <v>0</v>
@@ -3550,32 +3542,32 @@
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F40" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G40" s="15" t="inlineStr">
@@ -3585,32 +3577,32 @@
       </c>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J40" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K40" s="15" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="L40" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M40" s="15" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N40" s="16" t="n">
-        <v>175</v>
+        <v>2649.6</v>
       </c>
       <c r="O40" s="13" t="n">
         <v>0</v>
@@ -3622,12 +3614,12 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
@@ -3637,12 +3629,12 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -3657,7 +3649,7 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
@@ -3673,16 +3665,16 @@
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>775.6</v>
+        <v>175</v>
       </c>
       <c r="O41" s="13" t="n">
         <v>0</v>
@@ -3694,27 +3686,27 @@
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F42" s="15" t="inlineStr">
@@ -3729,12 +3721,12 @@
       </c>
       <c r="H42" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I42" s="15" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J42" s="15" t="n">
@@ -3745,16 +3737,16 @@
       </c>
       <c r="L42" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M42" s="15" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N42" s="16" t="n">
-        <v>5388.936</v>
+        <v>775.6</v>
       </c>
       <c r="O42" s="13" t="n">
         <v>0</v>
@@ -3766,27 +3758,27 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34081</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ERQUY</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 2 + Pax</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -3806,7 +3798,7 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
@@ -3817,16 +3809,16 @@
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34090</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00170724</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>177.5</v>
+        <v>5388.936</v>
       </c>
       <c r="O43" s="13" t="n">
         <v>0</v>
@@ -3838,27 +3830,27 @@
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34081</t>
         </is>
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
         </is>
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DE ERQUY</t>
         </is>
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GEODP 2 + Pax</t>
         </is>
       </c>
       <c r="F44" s="15" t="inlineStr">
@@ -3873,12 +3865,12 @@
       </c>
       <c r="H44" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I44" s="15" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J44" s="15" t="n">
@@ -3889,16 +3881,16 @@
       </c>
       <c r="L44" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34090</t>
         </is>
       </c>
       <c r="M44" s="15" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170724</t>
         </is>
       </c>
       <c r="N44" s="16" t="n">
-        <v>1700</v>
+        <v>177.5</v>
       </c>
       <c r="O44" s="13" t="n">
         <v>0</v>
@@ -3910,27 +3902,27 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34012</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Migration module Placier</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -3945,64 +3937,64 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34021</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00170494</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>1786.1</v>
+        <v>1700</v>
       </c>
       <c r="O45" s="13" t="n">
-        <v>909.9</v>
+        <v>0</v>
       </c>
       <c r="P45" s="12" t="n">
-        <v>303.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34012</t>
         </is>
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Migration module Placier</t>
         </is>
       </c>
       <c r="F46" s="15" t="inlineStr">
@@ -4022,64 +4014,64 @@
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="J46" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K46" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L46" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34021</t>
         </is>
       </c>
       <c r="M46" s="15" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170494</t>
         </is>
       </c>
       <c r="N46" s="16" t="n">
-        <v>170</v>
+        <v>1786.1</v>
       </c>
       <c r="O46" s="13" t="n">
-        <v>0</v>
+        <v>909.9</v>
       </c>
       <c r="P46" s="16" t="n">
-        <v>0</v>
+        <v>303.3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
@@ -4089,32 +4081,32 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>3000</v>
+        <v>170</v>
       </c>
       <c r="O47" s="13" t="n">
         <v>0</v>
@@ -4126,27 +4118,27 @@
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F48" s="15" t="inlineStr">
@@ -4173,57 +4165,57 @@
         <v>4</v>
       </c>
       <c r="K48" s="15" t="n">
-        <v>2.25</v>
+        <v>6.25</v>
       </c>
       <c r="L48" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M48" s="15" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N48" s="16" t="n">
-        <v>1980</v>
+        <v>3000</v>
       </c>
       <c r="O48" s="13" t="n">
-        <v>308</v>
+        <v>0</v>
       </c>
       <c r="P48" s="16" t="n">
-        <v>136.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP ODP (Terrasse)</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -4233,64 +4225,64 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>700</v>
+        <v>1980</v>
       </c>
       <c r="O49" s="13" t="n">
-        <v>0</v>
+        <v>308</v>
       </c>
       <c r="P49" s="12" t="n">
-        <v>0</v>
+        <v>136.89</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="F50" s="15" t="inlineStr">
@@ -4321,16 +4313,16 @@
       </c>
       <c r="L50" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="M50" s="15" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="N50" s="16" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="O50" s="13" t="n">
         <v>0</v>
@@ -4342,32 +4334,32 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -4377,32 +4369,32 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>186.235</v>
+        <v>170</v>
       </c>
       <c r="O51" s="13" t="n">
         <v>0</v>
@@ -4414,12 +4406,12 @@
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C52" s="15" t="inlineStr">
@@ -4429,12 +4421,12 @@
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F52" s="15" t="inlineStr">
@@ -4461,20 +4453,20 @@
         <v>4</v>
       </c>
       <c r="K52" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L52" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M52" s="15" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N52" s="16" t="n">
-        <v>1890</v>
+        <v>186.235</v>
       </c>
       <c r="O52" s="13" t="n">
         <v>0</v>
@@ -4486,27 +4478,27 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commande modélisation supplémentaire </t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -4526,27 +4518,27 @@
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>400</v>
+        <v>1890</v>
       </c>
       <c r="O53" s="13" t="n">
         <v>0</v>
@@ -4558,12 +4550,12 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C54" s="15" t="inlineStr">
@@ -4573,12 +4565,12 @@
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F54" s="15" t="inlineStr">
@@ -4598,27 +4590,27 @@
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J54" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K54" s="15" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="L54" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M54" s="15" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N54" s="16" t="n">
-        <v>552</v>
+        <v>400</v>
       </c>
       <c r="O54" s="13" t="n">
         <v>0</v>
@@ -4630,32 +4622,32 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -4670,27 +4662,27 @@
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>203.5</v>
+        <v>552</v>
       </c>
       <c r="O55" s="13" t="n">
         <v>0</v>
@@ -4702,27 +4694,27 @@
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E56" s="15" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F56" s="15" t="inlineStr">
@@ -4737,32 +4729,32 @@
       </c>
       <c r="H56" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I56" s="15" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J56" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K56" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M56" s="15" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N56" s="16" t="n">
-        <v>2000</v>
+        <v>203.5</v>
       </c>
       <c r="O56" s="13" t="n">
         <v>0</v>
@@ -4774,27 +4766,27 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33500</t>
+          <t>PDMDEP-33517</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
+          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mairie de Carcès </t>
+          <t>VILLE DE MONTREUIL</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -4825,16 +4817,16 @@
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33509</t>
+          <t>PDMDEP-33526</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00168117</t>
+          <t>00168179</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>203.5</v>
+        <v>2000</v>
       </c>
       <c r="O57" s="13" t="n">
         <v>0</v>
@@ -4846,32 +4838,32 @@
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33500</t>
         </is>
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t xml:space="preserve">Mairie de Carcès </t>
         </is>
       </c>
       <c r="E58" s="15" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="F58" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G58" s="15" t="inlineStr">
@@ -4881,12 +4873,12 @@
       </c>
       <c r="H58" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J58" s="15" t="n">
@@ -4897,16 +4889,16 @@
       </c>
       <c r="L58" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33509</t>
         </is>
       </c>
       <c r="M58" s="15" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168117</t>
         </is>
       </c>
       <c r="N58" s="16" t="n">
-        <v>171.4</v>
+        <v>203.5</v>
       </c>
       <c r="O58" s="13" t="n">
         <v>0</v>
@@ -4918,27 +4910,27 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33451</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE CHATELLERAULT] - FDS pour Littéralis Expert</t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE CHATELLERAULT</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>FDS pour Littéralis Expert</t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -4969,16 +4961,16 @@
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33455</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00167958</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>400</v>
+        <v>171.4</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>0</v>
@@ -4990,32 +4982,32 @@
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33451</t>
         </is>
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
+          <t>[VILLE DE CHATELLERAULT] - FDS pour Littéralis Expert</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>VILLE DE CHATELLERAULT</t>
         </is>
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t>FDS pour Littéralis Expert</t>
         </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G60" s="15" t="inlineStr">
@@ -5025,12 +5017,12 @@
       </c>
       <c r="H60" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J60" s="15" t="n">
@@ -5041,16 +5033,16 @@
       </c>
       <c r="L60" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33455</t>
         </is>
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00167958</t>
         </is>
       </c>
       <c r="N60" s="16" t="n">
-        <v>6177.52</v>
+        <v>400</v>
       </c>
       <c r="O60" s="13" t="n">
         <v>0</v>
@@ -5062,27 +5054,27 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -5097,12 +5089,12 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
@@ -5113,16 +5105,16 @@
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>500</v>
+        <v>6177.52</v>
       </c>
       <c r="O61" s="13" t="n">
         <v>0</v>
@@ -5134,37 +5126,37 @@
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33304</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E62" s="15" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F62" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G62" s="15" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H62" s="15" t="inlineStr">
@@ -5174,21 +5166,29 @@
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J62" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K62" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L62" s="15" t="inlineStr"/>
-      <c r="M62" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L62" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33401</t>
+        </is>
+      </c>
+      <c r="M62" s="15" t="inlineStr">
+        <is>
+          <t>00167624</t>
+        </is>
+      </c>
       <c r="N62" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" s="16" t="n">
+        <v>500</v>
+      </c>
+      <c r="O62" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P62" s="16" t="n">
@@ -5198,37 +5198,37 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33304</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
@@ -5238,29 +5238,21 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33272</t>
-        </is>
-      </c>
-      <c r="M63" s="11" t="inlineStr">
-        <is>
-          <t>00166910</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L63" s="11" t="inlineStr"/>
+      <c r="M63" s="11" t="inlineStr"/>
       <c r="N63" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P63" s="12" t="n">
@@ -5270,27 +5262,27 @@
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr">
@@ -5305,12 +5297,12 @@
       </c>
       <c r="H64" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J64" s="15" t="n">
@@ -5321,16 +5313,16 @@
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N64" s="16" t="n">
-        <v>149</v>
+        <v>240</v>
       </c>
       <c r="O64" s="13" t="n">
         <v>0</v>
@@ -5342,32 +5334,32 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
@@ -5377,32 +5369,32 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>337.5</v>
+        <v>149</v>
       </c>
       <c r="O65" s="13" t="n">
         <v>0</v>
@@ -5465,16 +5457,16 @@
       </c>
       <c r="L66" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N66" s="16" t="n">
-        <v>320</v>
+        <v>337.5</v>
       </c>
       <c r="O66" s="13" t="n">
         <v>0</v>
@@ -5486,32 +5478,32 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33149</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
@@ -5521,32 +5513,32 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33158</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00165719</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>1047</v>
+        <v>320</v>
       </c>
       <c r="O67" s="13" t="n">
         <v>0</v>
@@ -5558,32 +5550,32 @@
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33149</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP</t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G68" s="15" t="inlineStr">
@@ -5593,32 +5585,32 @@
       </c>
       <c r="H68" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J68" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K68" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33158</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165719</t>
         </is>
       </c>
       <c r="N68" s="16" t="n">
-        <v>400</v>
+        <v>1047</v>
       </c>
       <c r="O68" s="13" t="n">
         <v>0</v>
@@ -5630,32 +5622,32 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -5665,7 +5657,7 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
@@ -5677,20 +5669,20 @@
         <v>6</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="O69" s="13" t="n">
         <v>0</v>
@@ -5702,12 +5694,12 @@
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32732</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
@@ -5717,12 +5709,12 @@
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Caisse</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
@@ -5737,12 +5729,12 @@
       </c>
       <c r="H70" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I70" s="15" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J70" s="15" t="n">
@@ -5753,16 +5745,16 @@
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32741</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>00163789</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N70" s="16" t="n">
-        <v>680.8</v>
+        <v>200</v>
       </c>
       <c r="O70" s="13" t="n">
         <v>0</v>
@@ -5774,12 +5766,12 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32663</t>
+          <t>PDMDEP-32732</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
@@ -5789,12 +5781,12 @@
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LA GARDE</t>
+          <t>MAIRIE DE LA SENTINELLE</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Migration Placier</t>
+          <t>Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -5809,12 +5801,12 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
@@ -5825,16 +5817,16 @@
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32669</t>
+          <t>PDMDEP-32741</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00163456</t>
+          <t>00163789</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>2614.5</v>
+        <v>680.8</v>
       </c>
       <c r="O71" s="13" t="n">
         <v>0</v>
@@ -5846,32 +5838,32 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32663</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>COMMUNE DE LA GARDE</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Migration Placier</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G72" s="15" t="inlineStr">
@@ -5881,12 +5873,12 @@
       </c>
       <c r="H72" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="J72" s="15" t="n">
@@ -5897,16 +5889,16 @@
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32669</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00163456</t>
         </is>
       </c>
       <c r="N72" s="16" t="n">
-        <v>403.074</v>
+        <v>2614.5</v>
       </c>
       <c r="O72" s="13" t="n">
         <v>0</v>
@@ -5918,32 +5910,32 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32598</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Déploiement GeoDP Caisse</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
@@ -5953,7 +5945,7 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
@@ -5969,19 +5961,19 @@
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32607</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00163155</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" s="12" t="n">
-        <v>276</v>
+        <v>403.074</v>
+      </c>
+      <c r="O73" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="P73" s="12" t="n">
         <v>0</v>
@@ -5990,32 +5982,32 @@
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G74" s="15" t="inlineStr">
@@ -6025,12 +6017,12 @@
       </c>
       <c r="H74" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J74" s="15" t="n">
@@ -6041,19 +6033,19 @@
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32607</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163155</t>
         </is>
       </c>
       <c r="N74" s="16" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O74" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O74" s="16" t="n">
+        <v>276</v>
       </c>
       <c r="P74" s="16" t="n">
         <v>0</v>
@@ -6062,32 +6054,32 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
@@ -6097,32 +6089,32 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K75" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>11278.05</v>
+        <v>142.1</v>
       </c>
       <c r="O75" s="13" t="n">
         <v>0</v>
@@ -6134,32 +6126,32 @@
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32400</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G76" s="15" t="inlineStr">
@@ -6169,12 +6161,12 @@
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J76" s="15" t="n">
@@ -6185,16 +6177,16 @@
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32406</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>00161680</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N76" s="16" t="n">
-        <v>1000</v>
+        <v>11278.05</v>
       </c>
       <c r="O76" s="13" t="n">
         <v>0</v>
@@ -6206,32 +6198,32 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32366</t>
+          <t>PDMDEP-32400</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
+          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>Commune de Pleneuf Val André</t>
+          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
@@ -6241,7 +6233,7 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
@@ -6257,16 +6249,16 @@
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32372</t>
+          <t>PDMDEP-32406</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00161594</t>
+          <t>00161680</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="O77" s="13" t="n">
         <v>0</v>
@@ -6278,12 +6270,12 @@
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32366</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
@@ -6293,12 +6285,12 @@
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>Commune de Pleneuf Val André</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
@@ -6318,7 +6310,7 @@
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J78" s="15" t="n">
@@ -6329,16 +6321,16 @@
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32372</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161594</t>
         </is>
       </c>
       <c r="N78" s="16" t="n">
-        <v>450</v>
+        <v>220</v>
       </c>
       <c r="O78" s="13" t="n">
         <v>0</v>
@@ -6350,32 +6342,32 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
@@ -6385,32 +6377,32 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O79" s="13" t="n">
         <v>0</v>
@@ -6422,32 +6414,32 @@
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32193</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTAUBAN</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP2</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G80" s="15" t="inlineStr">
@@ -6457,32 +6449,32 @@
       </c>
       <c r="H80" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J80" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K80" s="15" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="L80" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32202</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M80" s="15" t="inlineStr">
         <is>
-          <t>00160782</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N80" s="16" t="n">
-        <v>3240</v>
+        <v>910</v>
       </c>
       <c r="O80" s="13" t="n">
         <v>0</v>
@@ -6494,27 +6486,27 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32193</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE MONTAUBAN</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Migration GEODP2</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
@@ -6534,7 +6526,7 @@
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
@@ -6545,16 +6537,16 @@
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32202</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160782</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>1050</v>
+        <v>3240</v>
       </c>
       <c r="O81" s="13" t="n">
         <v>0</v>
@@ -6566,27 +6558,27 @@
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
@@ -6606,7 +6598,7 @@
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J82" s="15" t="n">
@@ -6617,16 +6609,16 @@
       </c>
       <c r="L82" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M82" s="15" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N82" s="16" t="n">
-        <v>433.5</v>
+        <v>1050</v>
       </c>
       <c r="O82" s="13" t="n">
         <v>0</v>
@@ -6638,32 +6630,32 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -6673,34 +6665,34 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" s="12" t="n">
+        <v>433.5</v>
+      </c>
+      <c r="O83" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P83" s="12" t="n">
@@ -6710,32 +6702,32 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G84" s="15" t="inlineStr">
@@ -6745,34 +6737,34 @@
       </c>
       <c r="H84" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J84" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K84" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L84" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M84" s="15" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N84" s="16" t="n">
-        <v>285</v>
-      </c>
-      <c r="O84" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P84" s="16" t="n">
@@ -6782,32 +6774,32 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
@@ -6822,7 +6814,7 @@
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
@@ -6833,16 +6825,16 @@
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>120</v>
+        <v>285</v>
       </c>
       <c r="O85" s="13" t="n">
         <v>0</v>
@@ -6854,32 +6846,32 @@
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G86" s="15" t="inlineStr">
@@ -6889,12 +6881,12 @@
       </c>
       <c r="H86" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J86" s="15" t="n">
@@ -6905,16 +6897,16 @@
       </c>
       <c r="L86" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M86" s="15" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N86" s="16" t="n">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="O86" s="13" t="n">
         <v>0</v>
@@ -6926,27 +6918,27 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
@@ -6961,32 +6953,32 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K87" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>203.5</v>
+        <v>210</v>
       </c>
       <c r="O87" s="13" t="n">
         <v>0</v>
@@ -6998,32 +6990,32 @@
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G88" s="15" t="inlineStr">
@@ -7033,12 +7025,12 @@
       </c>
       <c r="H88" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J88" s="15" t="n">
@@ -7049,16 +7041,16 @@
       </c>
       <c r="L88" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M88" s="15" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N88" s="16" t="n">
-        <v>1088.5</v>
+        <v>203.5</v>
       </c>
       <c r="O88" s="13" t="n">
         <v>0</v>
@@ -7070,32 +7062,32 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr">
@@ -7105,12 +7097,12 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
@@ -7121,16 +7113,16 @@
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31488</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00157472</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>130</v>
+        <v>1088.5</v>
       </c>
       <c r="O89" s="13" t="n">
         <v>0</v>
@@ -7142,12 +7134,12 @@
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31479</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
@@ -7157,7 +7149,7 @@
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
       <c r="E90" s="15" t="inlineStr">
@@ -7182,7 +7174,7 @@
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="J90" s="15" t="n">
@@ -7193,16 +7185,16 @@
       </c>
       <c r="L90" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31488</t>
         </is>
       </c>
       <c r="M90" s="15" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157472</t>
         </is>
       </c>
       <c r="N90" s="16" t="n">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="O90" s="13" t="n">
         <v>0</v>
@@ -7214,12 +7206,12 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
@@ -7229,12 +7221,12 @@
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
@@ -7254,7 +7246,7 @@
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
@@ -7265,16 +7257,16 @@
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="O91" s="13" t="n">
         <v>0</v>
@@ -7286,12 +7278,12 @@
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
@@ -7301,12 +7293,12 @@
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E92" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
@@ -7326,7 +7318,7 @@
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J92" s="15" t="n">
@@ -7337,16 +7329,16 @@
       </c>
       <c r="L92" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M92" s="15" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N92" s="16" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O92" s="13" t="n">
         <v>0</v>
@@ -7358,12 +7350,12 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
@@ -7373,12 +7365,12 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
@@ -7398,27 +7390,27 @@
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K93" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O93" s="13" t="n">
         <v>0</v>
@@ -7430,32 +7422,32 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G94" s="15" t="inlineStr">
@@ -7465,32 +7457,32 @@
       </c>
       <c r="H94" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J94" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K94" s="15" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M94" s="15" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N94" s="16" t="n">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="O94" s="13" t="n">
         <v>0</v>
@@ -7502,12 +7494,12 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29964</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
@@ -7517,12 +7509,12 @@
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>SAINT DIZIER</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -7542,29 +7534,29 @@
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29965</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00152739</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="O95" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P95" s="12" t="n">
@@ -7574,27 +7566,27 @@
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-29964</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>SAINT DIZIER</t>
         </is>
       </c>
       <c r="E96" s="15" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
@@ -7621,22 +7613,22 @@
         <v>9</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>3.25</v>
+        <v>0.5</v>
       </c>
       <c r="L96" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-29965</t>
         </is>
       </c>
       <c r="M96" s="15" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00152739</t>
         </is>
       </c>
       <c r="N96" s="16" t="n">
-        <v>204.14</v>
-      </c>
-      <c r="O96" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P96" s="16" t="n">
@@ -7646,26 +7638,28 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
-        </is>
-      </c>
-      <c r="E97" s="11" t="n">
-        <v/>
+          <t>MAIRE DE PONTARLIER</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
+        </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
@@ -7684,29 +7678,29 @@
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>0.5</v>
+        <v>3.25</v>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" s="12" t="n">
+        <v>204.14</v>
+      </c>
+      <c r="O97" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P97" s="12" t="n">
@@ -7716,12 +7710,12 @@
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
@@ -7731,7 +7725,7 @@
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
+          <t>COMMUNE DE CARCASSONNE</t>
         </is>
       </c>
       <c r="E98" s="15" t="n">
@@ -7749,34 +7743,34 @@
       </c>
       <c r="H98" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I98" s="15" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J98" s="15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K98" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N98" s="16" t="n">
-        <v>401.54</v>
-      </c>
-      <c r="O98" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P98" s="16" t="n">
@@ -7786,12 +7780,12 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
@@ -7801,13 +7795,11 @@
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E99" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="n">
+        <v/>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
@@ -7826,27 +7818,27 @@
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
-        <v>275</v>
+        <v>401.54</v>
       </c>
       <c r="O99" s="13" t="n">
         <v>0</v>
@@ -7905,22 +7897,22 @@
         <v>11</v>
       </c>
       <c r="K100" s="15" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N100" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" s="16" t="n">
+        <v>275</v>
+      </c>
+      <c r="O100" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P100" s="16" t="n">
@@ -7977,22 +7969,22 @@
         <v>11</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
-        <v>1790</v>
-      </c>
-      <c r="O101" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P101" s="12" t="n">
@@ -8049,22 +8041,22 @@
         <v>11</v>
       </c>
       <c r="K102" s="15" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N102" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" s="16" t="n">
+        <v>1790</v>
+      </c>
+      <c r="O102" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="16" t="n">
@@ -8121,16 +8113,16 @@
         <v>11</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
@@ -8146,12 +8138,12 @@
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
@@ -8161,11 +8153,13 @@
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E104" s="15" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E104" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F104" s="15" t="inlineStr">
         <is>
@@ -8184,29 +8178,29 @@
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J104" s="15" t="n">
         <v>11</v>
       </c>
       <c r="K104" s="15" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N104" s="16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O104" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="16" t="n">
@@ -8216,12 +8210,12 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
@@ -8231,7 +8225,7 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -8249,32 +8243,32 @@
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="O105" s="13" t="n">
         <v>0</v>
@@ -8286,22 +8280,22 @@
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24531</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>[CD 17] - Paramétrage de redevances 3J</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E106" s="15" t="n">
@@ -8324,44 +8318,44 @@
       </c>
       <c r="I106" s="15" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J106" s="15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K106" s="15" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27992</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>502114</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N106" s="16" t="n">
-        <v>3016.08</v>
+        <v>460</v>
       </c>
       <c r="O106" s="13" t="n">
-        <v>418.9</v>
+        <v>0</v>
       </c>
       <c r="P106" s="16" t="n">
-        <v>69.81999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-24531</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>[CD 17] - Paramétrage de redevances 3J</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
@@ -8371,7 +8365,7 @@
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -8394,54 +8388,54 @@
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>0.25</v>
+        <v>6</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-27992</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>1200</v>
+        <v>3016.08</v>
       </c>
       <c r="O107" s="13" t="n">
-        <v>0</v>
+        <v>418.9</v>
       </c>
       <c r="P107" s="12" t="n">
-        <v>0</v>
+        <v>69.81999999999999</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E108" s="15" t="n">
@@ -8459,32 +8453,32 @@
       </c>
       <c r="H108" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J108" s="15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K108" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
-        <v>3919.06</v>
+        <v>1200</v>
       </c>
       <c r="O108" s="13" t="n">
         <v>0</v>
@@ -8496,12 +8490,12 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
@@ -8511,7 +8505,7 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -8534,29 +8528,29 @@
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K109" s="11" t="n">
         <v>0.5</v>
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O109" s="12" t="n">
+        <v>3919.06</v>
+      </c>
+      <c r="O109" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P109" s="12" t="n">
@@ -8566,12 +8560,12 @@
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
@@ -8581,7 +8575,7 @@
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E110" s="15" t="n">
@@ -8604,23 +8598,23 @@
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J110" s="15" t="n">
         <v>15</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N110" s="16" t="n">
@@ -8685,12 +8679,12 @@
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
@@ -8721,7 +8715,7 @@
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E112" s="15" t="n">
@@ -8755,12 +8749,12 @@
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M112" s="15" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N112" s="16" t="n">
@@ -8791,7 +8785,7 @@
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -8825,12 +8819,12 @@
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M113" s="11" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N113" s="12" t="n">
@@ -8846,12 +8840,12 @@
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
@@ -8861,7 +8855,7 @@
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E114" s="15" t="n">
@@ -8879,34 +8873,34 @@
       </c>
       <c r="H114" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J114" s="15" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K114" s="15" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N114" s="16" t="n">
-        <v>250</v>
-      </c>
-      <c r="O114" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="16" t="n">
@@ -8916,22 +8910,22 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -8954,27 +8948,27 @@
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
         <v>18</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N115" s="12" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="O115" s="13" t="n">
         <v>0</v>
@@ -8986,12 +8980,12 @@
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
@@ -9001,7 +8995,7 @@
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E116" s="15" t="n">
@@ -9019,34 +9013,34 @@
       </c>
       <c r="H116" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J116" s="15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K116" s="15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L116" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M116" s="15" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N116" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O116" s="16" t="n">
+        <v>230</v>
+      </c>
+      <c r="O116" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P116" s="16" t="n">
@@ -9056,12 +9050,12 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
@@ -9071,7 +9065,7 @@
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -9094,23 +9088,23 @@
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
         <v>19</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M117" s="11" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N117" s="12" t="n">
@@ -9126,12 +9120,12 @@
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18954</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
@@ -9141,13 +9135,11 @@
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>Maisons-Alfort</t>
-        </is>
-      </c>
-      <c r="E118" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+        </is>
+      </c>
+      <c r="E118" s="15" t="n">
+        <v/>
       </c>
       <c r="F118" s="15" t="inlineStr">
         <is>
@@ -9156,27 +9148,35 @@
       </c>
       <c r="G118" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H118" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J118" s="15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K118" s="15" t="n">
         <v>0.25</v>
       </c>
-      <c r="L118" s="15" t="inlineStr"/>
-      <c r="M118" s="15" t="inlineStr"/>
+      <c r="L118" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27377</t>
+        </is>
+      </c>
+      <c r="M118" s="15" t="inlineStr">
+        <is>
+          <t>478048</t>
+        </is>
+      </c>
       <c r="N118" s="16" t="n">
         <v>0</v>
       </c>
@@ -9190,26 +9190,28 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-18954</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
-        </is>
-      </c>
-      <c r="E119" s="11" t="n">
-        <v/>
+          <t>Maisons-Alfort</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F119" s="11" t="inlineStr">
         <is>
@@ -9228,11 +9230,11 @@
       </c>
       <c r="I119" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>05/02/2025</t>
         </is>
       </c>
       <c r="J119" s="11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K119" s="11" t="n">
         <v>0.25</v>
@@ -9252,22 +9254,22 @@
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E120" s="15" t="n">
@@ -9285,7 +9287,7 @@
       </c>
       <c r="H120" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I120" s="15" t="inlineStr">
@@ -9297,7 +9299,7 @@
         <v>22</v>
       </c>
       <c r="K120" s="15" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L120" s="15" t="inlineStr"/>
       <c r="M120" s="15" t="inlineStr"/>
@@ -9314,22 +9316,22 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -9337,44 +9339,36 @@
       </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G121" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J121" s="11" t="n">
         <v>22</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M121" s="11" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L121" s="11" t="inlineStr"/>
+      <c r="M121" s="11" t="inlineStr"/>
       <c r="N121" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O121" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P121" s="12" t="n">
@@ -9384,22 +9378,22 @@
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C122" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E122" s="15" t="n">
@@ -9407,7 +9401,7 @@
       </c>
       <c r="F122" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G122" s="15" t="inlineStr">
@@ -9417,12 +9411,12 @@
       </c>
       <c r="H122" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J122" s="15" t="n">
@@ -9433,16 +9427,16 @@
       </c>
       <c r="L122" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M122" s="15" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N122" s="16" t="n">
-        <v>557.145</v>
+        <v>240</v>
       </c>
       <c r="O122" s="13" t="n">
         <v>0</v>
@@ -9454,22 +9448,22 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -9482,7 +9476,7 @@
       </c>
       <c r="G123" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H123" s="11" t="inlineStr">
@@ -9492,21 +9486,29 @@
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L123" s="11" t="inlineStr"/>
-      <c r="M123" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L123" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M123" s="11" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N123" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O123" s="12" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O123" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P123" s="12" t="n">
@@ -9516,22 +9518,22 @@
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C124" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E124" s="15" t="n">
@@ -9554,14 +9556,14 @@
       </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J124" s="15" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="K124" s="15" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="L124" s="15" t="inlineStr"/>
       <c r="M124" s="15" t="inlineStr"/>
@@ -9578,12 +9580,12 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
@@ -9593,7 +9595,7 @@
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
@@ -9611,19 +9613,19 @@
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
         <v>35</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="L125" s="11" t="inlineStr"/>
       <c r="M125" s="11" t="inlineStr"/>
@@ -9640,22 +9642,22 @@
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E126" s="15" t="n">
@@ -9671,17 +9673,21 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H126" s="15" t="inlineStr"/>
+      <c r="H126" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I126" s="15" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J126" s="15" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L126" s="15" t="inlineStr"/>
       <c r="M126" s="15" t="inlineStr"/>
@@ -9698,12 +9704,12 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
@@ -9713,7 +9719,7 @@
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -9729,32 +9735,20 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H127" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H127" s="11" t="inlineStr"/>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="L127" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M127" s="11" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L127" s="11" t="inlineStr"/>
+      <c r="M127" s="11" t="inlineStr"/>
       <c r="N127" s="12" t="n">
         <v>0</v>
       </c>
@@ -9768,22 +9762,22 @@
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E128" s="15" t="n">
@@ -9796,29 +9790,33 @@
       </c>
       <c r="G128" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H128" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H128" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I128" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J128" s="15" t="n">
         <v>37</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>0.75</v>
+        <v>5.75</v>
       </c>
       <c r="L128" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-25456</t>
+          <t>PDMDEP-34532</t>
         </is>
       </c>
       <c r="M128" s="15" t="inlineStr">
         <is>
-          <t>424152</t>
+          <t>412263</t>
         </is>
       </c>
       <c r="N128" s="16" t="n">
@@ -9834,24 +9832,26 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12292</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C129" s="11" t="inlineStr"/>
+          <t>[CD06] Littéralis expert</t>
+        </is>
+      </c>
+      <c r="C129" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E129" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="n">
+        <v/>
       </c>
       <c r="F129" s="11" t="inlineStr">
         <is>
@@ -9860,17 +9860,13 @@
       </c>
       <c r="G129" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H129" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H129" s="11" t="inlineStr"/>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J129" s="11" t="n">
@@ -9879,8 +9875,16 @@
       <c r="K129" s="11" t="n">
         <v>0.75</v>
       </c>
-      <c r="L129" s="11" t="inlineStr"/>
-      <c r="M129" s="11" t="inlineStr"/>
+      <c r="L129" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-25456</t>
+        </is>
+      </c>
+      <c r="M129" s="11" t="inlineStr">
+        <is>
+          <t>424152</t>
+        </is>
+      </c>
       <c r="N129" s="12" t="n">
         <v>0</v>
       </c>
@@ -9894,21 +9898,25 @@
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>PSC-1363</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr"/>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
-        </is>
-      </c>
-      <c r="E130" s="15" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E130" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F130" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -9916,20 +9924,24 @@
       </c>
       <c r="G130" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H130" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H130" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I130" s="15" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J130" s="15" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="K130" s="15" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L130" s="15" t="inlineStr"/>
       <c r="M130" s="15" t="inlineStr"/>
@@ -9946,18 +9958,18 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>PSC-1351</t>
+          <t>PSC-1363</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>MAIRIE DE CADENET</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr"/>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>MAIRIE DE CADENET</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr"/>
@@ -9974,11 +9986,11 @@
       <c r="H131" s="11" t="inlineStr"/>
       <c r="I131" s="11" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="J131" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K131" s="11" t="n">
         <v>0.25</v>
@@ -9998,18 +10010,18 @@
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>PSC-1346</t>
+          <t>PSC-1351</t>
         </is>
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="C132" s="15" t="inlineStr"/>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="E132" s="15" t="inlineStr"/>
@@ -10026,7 +10038,7 @@
       <c r="H132" s="15" t="inlineStr"/>
       <c r="I132" s="15" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="J132" s="15" t="n">
@@ -10050,18 +10062,18 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PSC-1346</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr"/>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr"/>
@@ -10072,35 +10084,27 @@
       </c>
       <c r="G133" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H133" s="11" t="inlineStr"/>
       <c r="I133" s="11" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="J133" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K133" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
-      <c r="M133" s="11" t="inlineStr">
-        <is>
-          <t>00177354</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L133" s="11" t="inlineStr"/>
+      <c r="M133" s="11" t="inlineStr"/>
       <c r="N133" s="12" t="n">
-        <v>450</v>
-      </c>
-      <c r="O133" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P133" s="12" t="n">
@@ -10110,18 +10114,18 @@
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C134" s="15" t="inlineStr"/>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E134" s="15" t="inlineStr"/>
@@ -10132,27 +10136,35 @@
       </c>
       <c r="G134" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H134" s="15" t="inlineStr"/>
       <c r="I134" s="15" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J134" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K134" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L134" s="15" t="inlineStr"/>
-      <c r="M134" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L134" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M134" s="15" t="inlineStr">
+        <is>
+          <t>00177354</t>
+        </is>
+      </c>
       <c r="N134" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O134" s="16" t="n">
+        <v>450</v>
+      </c>
+      <c r="O134" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P134" s="16" t="n">
@@ -10162,18 +10174,18 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr"/>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr"/>
@@ -10190,14 +10202,14 @@
       <c r="H135" s="11" t="inlineStr"/>
       <c r="I135" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J135" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="L135" s="11" t="inlineStr"/>
       <c r="M135" s="11" t="inlineStr"/>
@@ -10214,18 +10226,18 @@
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C136" s="15" t="inlineStr"/>
       <c r="D136" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E136" s="15" t="inlineStr"/>
@@ -10236,31 +10248,23 @@
       </c>
       <c r="G136" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H136" s="15" t="inlineStr"/>
       <c r="I136" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J136" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K136" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L136" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M136" s="15" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="L136" s="15" t="inlineStr"/>
+      <c r="M136" s="15" t="inlineStr"/>
       <c r="N136" s="16" t="n">
         <v>0</v>
       </c>
@@ -10274,18 +10278,18 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>PSC-1047</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr"/>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E137" s="11" t="inlineStr"/>
@@ -10302,61 +10306,121 @@
       <c r="H137" s="11" t="inlineStr"/>
       <c r="I137" s="11" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J137" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K137" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L137" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M137" s="11" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N137" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1047</t>
+        </is>
+      </c>
+      <c r="B138" s="15" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="C138" s="15" t="inlineStr"/>
+      <c r="D138" s="15" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E138" s="15" t="inlineStr"/>
+      <c r="F138" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G138" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H138" s="15" t="inlineStr"/>
+      <c r="I138" s="15" t="inlineStr">
+        <is>
           <t>04/11/2025</t>
         </is>
       </c>
-      <c r="J137" s="11" t="n">
+      <c r="J138" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="K137" s="11" t="n">
+      <c r="K138" s="15" t="n">
         <v>0.25</v>
       </c>
-      <c r="L137" s="11" t="inlineStr">
+      <c r="L138" s="15" t="inlineStr">
         <is>
           <t>PDMDEP-26768</t>
         </is>
       </c>
-      <c r="M137" s="11" t="inlineStr">
+      <c r="M138" s="15" t="inlineStr">
         <is>
           <t>00141775</t>
         </is>
       </c>
-      <c r="N137" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O137" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P137" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="17" t="inlineStr">
+      <c r="N138" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B138" s="17" t="inlineStr"/>
-      <c r="C138" s="17" t="inlineStr"/>
-      <c r="D138" s="17" t="inlineStr"/>
-      <c r="E138" s="17" t="inlineStr"/>
-      <c r="F138" s="17" t="inlineStr"/>
-      <c r="G138" s="17" t="inlineStr"/>
-      <c r="H138" s="17" t="inlineStr"/>
-      <c r="I138" s="17" t="inlineStr"/>
-      <c r="J138" s="17" t="inlineStr"/>
-      <c r="K138" s="17" t="inlineStr"/>
-      <c r="L138" s="17" t="inlineStr"/>
-      <c r="M138" s="17" t="inlineStr"/>
-      <c r="N138" s="18" t="n">
+      <c r="B139" s="17" t="inlineStr"/>
+      <c r="C139" s="17" t="inlineStr"/>
+      <c r="D139" s="17" t="inlineStr"/>
+      <c r="E139" s="17" t="inlineStr"/>
+      <c r="F139" s="17" t="inlineStr"/>
+      <c r="G139" s="17" t="inlineStr"/>
+      <c r="H139" s="17" t="inlineStr"/>
+      <c r="I139" s="17" t="inlineStr"/>
+      <c r="J139" s="17" t="inlineStr"/>
+      <c r="K139" s="17" t="inlineStr"/>
+      <c r="L139" s="17" t="inlineStr"/>
+      <c r="M139" s="17" t="inlineStr"/>
+      <c r="N139" s="18" t="n">
         <v>121514.862</v>
       </c>
-      <c r="O138" s="18" t="n">
+      <c r="O139" s="18" t="n">
         <v>3355.2</v>
       </c>
-      <c r="P138" s="18" t="n">
-        <v>37.25</v>
+      <c r="P139" s="18" t="n">
+        <v>34.92</v>
       </c>
     </row>
   </sheetData>
@@ -10495,6 +10559,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId131"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId134"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11306,16 +11371,16 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>56.75</v>
+        <v>59</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>11.75</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>2.58</v>
+        <v>3.33</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>71.08</v>
+        <v>74.08</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>7.75</v>
@@ -11325,7 +11390,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14.6%</t>
         </is>
       </c>
     </row>
@@ -11342,10 +11407,10 @@
         <v>0</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -11355,7 +11420,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>9.4%</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11432,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>36.08</v>
+        <v>37.33</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-10-09.xlsx
+++ b/jira_export_2026-10-09.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>143 h</t>
+          <t>148 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P139"/>
+  <dimension ref="A1:P140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -949,7 +949,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -2021,7 +2021,7 @@
         <v>1</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L18" s="15" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>4</v>
       </c>
       <c r="K40" s="15" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="L40" s="15" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>4</v>
       </c>
       <c r="K48" s="15" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="L48" s="15" t="inlineStr">
         <is>
@@ -5198,12 +5198,12 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33304</t>
+          <t>PDMDEP-33311</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
+          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>AMIENS METROPOLE</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
@@ -5238,17 +5238,25 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L63" s="11" t="inlineStr"/>
-      <c r="M63" s="11" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L63" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33315</t>
+        </is>
+      </c>
+      <c r="M63" s="11" t="inlineStr">
+        <is>
+          <t>00167138</t>
+        </is>
+      </c>
       <c r="N63" s="12" t="n">
         <v>0</v>
       </c>
@@ -5262,37 +5270,37 @@
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33304</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G64" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H64" s="15" t="inlineStr">
@@ -5302,29 +5310,21 @@
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="J64" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K64" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33272</t>
-        </is>
-      </c>
-      <c r="M64" s="15" t="inlineStr">
-        <is>
-          <t>00166910</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L64" s="15" t="inlineStr"/>
+      <c r="M64" s="15" t="inlineStr"/>
       <c r="N64" s="16" t="n">
-        <v>240</v>
-      </c>
-      <c r="O64" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P64" s="16" t="n">
@@ -5334,27 +5334,27 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
@@ -5385,16 +5385,16 @@
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>149</v>
+        <v>240</v>
       </c>
       <c r="O65" s="13" t="n">
         <v>0</v>
@@ -5406,32 +5406,32 @@
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G66" s="15" t="inlineStr">
@@ -5441,32 +5441,32 @@
       </c>
       <c r="H66" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I66" s="15" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J66" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K66" s="15" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L66" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N66" s="16" t="n">
-        <v>337.5</v>
+        <v>149</v>
       </c>
       <c r="O66" s="13" t="n">
         <v>0</v>
@@ -5525,20 +5525,20 @@
         <v>5</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>320</v>
+        <v>337.5</v>
       </c>
       <c r="O67" s="13" t="n">
         <v>0</v>
@@ -5550,32 +5550,32 @@
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33149</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>Migration GeODP</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G68" s="15" t="inlineStr">
@@ -5585,32 +5585,32 @@
       </c>
       <c r="H68" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J68" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K68" s="15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33158</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>00165719</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N68" s="16" t="n">
-        <v>1047</v>
+        <v>320</v>
       </c>
       <c r="O68" s="13" t="n">
         <v>0</v>
@@ -5622,32 +5622,32 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33149</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -5657,32 +5657,32 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33158</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165719</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>400</v>
+        <v>1047</v>
       </c>
       <c r="O69" s="13" t="n">
         <v>0</v>
@@ -5694,32 +5694,32 @@
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G70" s="15" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="H70" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I70" s="15" t="inlineStr">
@@ -5741,20 +5741,20 @@
         <v>6</v>
       </c>
       <c r="K70" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N70" s="16" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="O70" s="13" t="n">
         <v>0</v>
@@ -5766,12 +5766,12 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32732</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Caisse</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
@@ -5817,16 +5817,16 @@
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32741</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00163789</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>680.8</v>
+        <v>200</v>
       </c>
       <c r="O71" s="13" t="n">
         <v>0</v>
@@ -5838,12 +5838,12 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32663</t>
+          <t>PDMDEP-32732</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LA GARDE</t>
+          <t>MAIRIE DE LA SENTINELLE</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>Migration Placier</t>
+          <t>Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="H72" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J72" s="15" t="n">
@@ -5889,16 +5889,16 @@
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32669</t>
+          <t>PDMDEP-32741</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>00163456</t>
+          <t>00163789</t>
         </is>
       </c>
       <c r="N72" s="16" t="n">
-        <v>2614.5</v>
+        <v>680.8</v>
       </c>
       <c r="O72" s="13" t="n">
         <v>0</v>
@@ -5910,32 +5910,32 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32663</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>COMMUNE DE LA GARDE</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Migration Placier</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
@@ -5961,16 +5961,16 @@
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32669</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00163456</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>403.074</v>
+        <v>2614.5</v>
       </c>
       <c r="O73" s="13" t="n">
         <v>0</v>
@@ -5982,32 +5982,32 @@
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32598</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>Déploiement GeoDP Caisse</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G74" s="15" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="H74" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I74" s="15" t="inlineStr">
@@ -6033,19 +6033,19 @@
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32607</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>00163155</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N74" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="16" t="n">
-        <v>276</v>
+        <v>403.074</v>
+      </c>
+      <c r="O74" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="P74" s="16" t="n">
         <v>0</v>
@@ -6054,32 +6054,32 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
@@ -6089,12 +6089,12 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
@@ -6105,19 +6105,19 @@
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32607</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163155</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O75" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O75" s="12" t="n">
+        <v>276</v>
       </c>
       <c r="P75" s="12" t="n">
         <v>0</v>
@@ -6126,32 +6126,32 @@
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G76" s="15" t="inlineStr">
@@ -6161,32 +6161,32 @@
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J76" s="15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K76" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N76" s="16" t="n">
-        <v>11278.05</v>
+        <v>142.1</v>
       </c>
       <c r="O76" s="13" t="n">
         <v>0</v>
@@ -6198,32 +6198,32 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32400</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
@@ -6249,16 +6249,16 @@
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32406</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00161680</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>1000</v>
+        <v>11278.05</v>
       </c>
       <c r="O77" s="13" t="n">
         <v>0</v>
@@ -6270,32 +6270,32 @@
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32366</t>
+          <t>PDMDEP-32400</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
+          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>Commune de Pleneuf Val André</t>
+          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G78" s="15" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="H78" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I78" s="15" t="inlineStr">
@@ -6321,16 +6321,16 @@
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32372</t>
+          <t>PDMDEP-32406</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>00161594</t>
+          <t>00161680</t>
         </is>
       </c>
       <c r="N78" s="16" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="O78" s="13" t="n">
         <v>0</v>
@@ -6342,12 +6342,12 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32366</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
@@ -6357,12 +6357,12 @@
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>Commune de Pleneuf Val André</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
@@ -6393,16 +6393,16 @@
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32372</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161594</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>450</v>
+        <v>220</v>
       </c>
       <c r="O79" s="13" t="n">
         <v>0</v>
@@ -6414,32 +6414,32 @@
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G80" s="15" t="inlineStr">
@@ -6449,32 +6449,32 @@
       </c>
       <c r="H80" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J80" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K80" s="15" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="L80" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M80" s="15" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N80" s="16" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O80" s="13" t="n">
         <v>0</v>
@@ -6486,32 +6486,32 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32193</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTAUBAN</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP2</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
@@ -6521,32 +6521,32 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32202</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00160782</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>3240</v>
+        <v>910</v>
       </c>
       <c r="O81" s="13" t="n">
         <v>0</v>
@@ -6558,27 +6558,27 @@
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32193</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE MONTAUBAN</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Migration GEODP2</t>
         </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
@@ -6598,7 +6598,7 @@
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="J82" s="15" t="n">
@@ -6609,16 +6609,16 @@
       </c>
       <c r="L82" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32202</t>
         </is>
       </c>
       <c r="M82" s="15" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160782</t>
         </is>
       </c>
       <c r="N82" s="16" t="n">
-        <v>1050</v>
+        <v>3240</v>
       </c>
       <c r="O82" s="13" t="n">
         <v>0</v>
@@ -6630,27 +6630,27 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
@@ -6681,16 +6681,16 @@
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>433.5</v>
+        <v>1050</v>
       </c>
       <c r="O83" s="13" t="n">
         <v>0</v>
@@ -6702,32 +6702,32 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G84" s="15" t="inlineStr">
@@ -6737,34 +6737,34 @@
       </c>
       <c r="H84" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J84" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K84" s="15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L84" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M84" s="15" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N84" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" s="16" t="n">
+        <v>433.5</v>
+      </c>
+      <c r="O84" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P84" s="16" t="n">
@@ -6774,32 +6774,32 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
@@ -6809,34 +6809,34 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>285</v>
-      </c>
-      <c r="O85" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P85" s="12" t="n">
@@ -6846,32 +6846,32 @@
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G86" s="15" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J86" s="15" t="n">
@@ -6897,16 +6897,16 @@
       </c>
       <c r="L86" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M86" s="15" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N86" s="16" t="n">
-        <v>120</v>
+        <v>285</v>
       </c>
       <c r="O86" s="13" t="n">
         <v>0</v>
@@ -6918,32 +6918,32 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
@@ -6969,16 +6969,16 @@
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="O87" s="13" t="n">
         <v>0</v>
@@ -6990,27 +6990,27 @@
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
@@ -7025,32 +7025,32 @@
       </c>
       <c r="H88" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J88" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K88" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M88" s="15" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N88" s="16" t="n">
-        <v>203.5</v>
+        <v>210</v>
       </c>
       <c r="O88" s="13" t="n">
         <v>0</v>
@@ -7062,32 +7062,32 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr">
@@ -7097,12 +7097,12 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
@@ -7113,16 +7113,16 @@
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>1088.5</v>
+        <v>203.5</v>
       </c>
       <c r="O89" s="13" t="n">
         <v>0</v>
@@ -7134,32 +7134,32 @@
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E90" s="15" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G90" s="15" t="inlineStr">
@@ -7169,12 +7169,12 @@
       </c>
       <c r="H90" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J90" s="15" t="n">
@@ -7185,16 +7185,16 @@
       </c>
       <c r="L90" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31488</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M90" s="15" t="inlineStr">
         <is>
-          <t>00157472</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N90" s="16" t="n">
-        <v>130</v>
+        <v>1088.5</v>
       </c>
       <c r="O90" s="13" t="n">
         <v>0</v>
@@ -7206,12 +7206,12 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31479</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
@@ -7257,16 +7257,16 @@
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31488</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157472</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="O91" s="13" t="n">
         <v>0</v>
@@ -7278,12 +7278,12 @@
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
@@ -7293,12 +7293,12 @@
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E92" s="15" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J92" s="15" t="n">
@@ -7329,16 +7329,16 @@
       </c>
       <c r="L92" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M92" s="15" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N92" s="16" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="O92" s="13" t="n">
         <v>0</v>
@@ -7350,12 +7350,12 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
@@ -7401,16 +7401,16 @@
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O93" s="13" t="n">
         <v>0</v>
@@ -7422,12 +7422,12 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
@@ -7462,27 +7462,27 @@
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J94" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K94" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M94" s="15" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N94" s="16" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O94" s="13" t="n">
         <v>0</v>
@@ -7494,32 +7494,32 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G95" s="11" t="inlineStr">
@@ -7529,32 +7529,32 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="O95" s="13" t="n">
         <v>0</v>
@@ -7566,12 +7566,12 @@
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29964</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>SAINT DIZIER</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E96" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
@@ -7606,29 +7606,29 @@
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J96" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L96" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29965</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M96" s="15" t="inlineStr">
         <is>
-          <t>00152739</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N96" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="16" t="n">
+        <v>230</v>
+      </c>
+      <c r="O96" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P96" s="16" t="n">
@@ -7638,27 +7638,27 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-29964</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>SAINT DIZIER</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
@@ -7685,22 +7685,22 @@
         <v>9</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>3.25</v>
+        <v>0.5</v>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-29965</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00152739</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
-        <v>204.14</v>
-      </c>
-      <c r="O97" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P97" s="12" t="n">
@@ -7710,26 +7710,28 @@
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
-        </is>
-      </c>
-      <c r="E98" s="15" t="n">
-        <v/>
+          <t>MAIRE DE PONTARLIER</t>
+        </is>
+      </c>
+      <c r="E98" s="15" t="inlineStr">
+        <is>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
+        </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
         <is>
@@ -7748,29 +7750,29 @@
       </c>
       <c r="I98" s="15" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J98" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K98" s="15" t="n">
-        <v>0.5</v>
+        <v>3.25</v>
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N98" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" s="16" t="n">
+        <v>204.14</v>
+      </c>
+      <c r="O98" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P98" s="16" t="n">
@@ -7780,12 +7782,12 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
@@ -7795,7 +7797,7 @@
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
+          <t>COMMUNE DE CARCASSONNE</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -7813,34 +7815,34 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
-        <v>401.54</v>
-      </c>
-      <c r="O99" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P99" s="12" t="n">
@@ -7850,12 +7852,12 @@
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
@@ -7865,13 +7867,11 @@
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E100" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E100" s="15" t="n">
+        <v/>
       </c>
       <c r="F100" s="15" t="inlineStr">
         <is>
@@ -7890,27 +7890,27 @@
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J100" s="15" t="n">
         <v>11</v>
       </c>
       <c r="K100" s="15" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N100" s="16" t="n">
-        <v>275</v>
+        <v>401.54</v>
       </c>
       <c r="O100" s="13" t="n">
         <v>0</v>
@@ -7973,18 +7973,18 @@
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" s="12" t="n">
+        <v>275</v>
+      </c>
+      <c r="O101" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P101" s="12" t="n">
@@ -8045,18 +8045,18 @@
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N102" s="16" t="n">
-        <v>1790</v>
-      </c>
-      <c r="O102" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="16" t="n">
@@ -8117,18 +8117,18 @@
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" s="12" t="n">
+        <v>1790</v>
+      </c>
+      <c r="O103" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P103" s="12" t="n">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N104" s="16" t="n">
@@ -8210,12 +8210,12 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
@@ -8225,11 +8225,13 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E105" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
@@ -8248,29 +8250,29 @@
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O105" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="12" t="n">
@@ -8280,12 +8282,12 @@
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
@@ -8295,7 +8297,7 @@
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="E106" s="15" t="n">
@@ -8313,32 +8315,32 @@
       </c>
       <c r="H106" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I106" s="15" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J106" s="15" t="n">
         <v>11</v>
       </c>
       <c r="K106" s="15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N106" s="16" t="n">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="O106" s="13" t="n">
         <v>0</v>
@@ -8350,22 +8352,22 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24531</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[CD 17] - Paramétrage de redevances 3J</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -8388,44 +8390,44 @@
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27992</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>502114</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>3016.08</v>
+        <v>460</v>
       </c>
       <c r="O107" s="13" t="n">
-        <v>418.9</v>
+        <v>0</v>
       </c>
       <c r="P107" s="12" t="n">
-        <v>69.81999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-24531</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>[CD 17] - Paramétrage de redevances 3J</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
@@ -8435,7 +8437,7 @@
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E108" s="15" t="n">
@@ -8458,54 +8460,54 @@
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="J108" s="15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K108" s="15" t="n">
-        <v>0.25</v>
+        <v>6</v>
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-27992</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
-        <v>1200</v>
+        <v>3016.08</v>
       </c>
       <c r="O108" s="13" t="n">
-        <v>0</v>
+        <v>418.9</v>
       </c>
       <c r="P108" s="16" t="n">
-        <v>0</v>
+        <v>69.81999999999999</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -8523,32 +8525,32 @@
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N109" s="12" t="n">
-        <v>3919.06</v>
+        <v>1200</v>
       </c>
       <c r="O109" s="13" t="n">
         <v>0</v>
@@ -8560,12 +8562,12 @@
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
@@ -8575,7 +8577,7 @@
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E110" s="15" t="n">
@@ -8598,29 +8600,29 @@
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J110" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K110" s="15" t="n">
         <v>0.5</v>
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N110" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O110" s="16" t="n">
+        <v>3919.06</v>
+      </c>
+      <c r="O110" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="16" t="n">
@@ -8630,12 +8632,12 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
@@ -8645,7 +8647,7 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -8668,23 +8670,23 @@
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
         <v>15</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
@@ -8749,12 +8751,12 @@
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M112" s="15" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N112" s="16" t="n">
@@ -8785,7 +8787,7 @@
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -8819,12 +8821,12 @@
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M113" s="11" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N113" s="12" t="n">
@@ -8855,7 +8857,7 @@
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E114" s="15" t="n">
@@ -8889,12 +8891,12 @@
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N114" s="16" t="n">
@@ -8910,12 +8912,12 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
@@ -8925,7 +8927,7 @@
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -8943,34 +8945,34 @@
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N115" s="12" t="n">
-        <v>250</v>
-      </c>
-      <c r="O115" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="12" t="n">
@@ -8980,22 +8982,22 @@
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E116" s="15" t="n">
@@ -9018,27 +9020,27 @@
       </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J116" s="15" t="n">
         <v>18</v>
       </c>
       <c r="K116" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L116" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M116" s="15" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N116" s="16" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="O116" s="13" t="n">
         <v>0</v>
@@ -9050,12 +9052,12 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
@@ -9065,7 +9067,7 @@
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -9083,34 +9085,34 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M117" s="11" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N117" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O117" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="O117" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P117" s="12" t="n">
@@ -9120,12 +9122,12 @@
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
@@ -9135,7 +9137,7 @@
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E118" s="15" t="n">
@@ -9158,23 +9160,23 @@
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J118" s="15" t="n">
         <v>19</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M118" s="15" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N118" s="16" t="n">
@@ -9190,12 +9192,12 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18954</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
@@ -9205,13 +9207,11 @@
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>Maisons-Alfort</t>
-        </is>
-      </c>
-      <c r="E119" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="n">
+        <v/>
       </c>
       <c r="F119" s="11" t="inlineStr">
         <is>
@@ -9220,27 +9220,35 @@
       </c>
       <c r="G119" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I119" s="11" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J119" s="11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K119" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L119" s="11" t="inlineStr"/>
-      <c r="M119" s="11" t="inlineStr"/>
+      <c r="L119" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27377</t>
+        </is>
+      </c>
+      <c r="M119" s="11" t="inlineStr">
+        <is>
+          <t>478048</t>
+        </is>
+      </c>
       <c r="N119" s="12" t="n">
         <v>0</v>
       </c>
@@ -9254,26 +9262,28 @@
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-18954</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
-        </is>
-      </c>
-      <c r="E120" s="15" t="n">
-        <v/>
+          <t>Maisons-Alfort</t>
+        </is>
+      </c>
+      <c r="E120" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F120" s="15" t="inlineStr">
         <is>
@@ -9292,11 +9302,11 @@
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>05/02/2025</t>
         </is>
       </c>
       <c r="J120" s="15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K120" s="15" t="n">
         <v>0.25</v>
@@ -9316,22 +9326,22 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -9349,7 +9359,7 @@
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
@@ -9361,7 +9371,7 @@
         <v>22</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L121" s="11" t="inlineStr"/>
       <c r="M121" s="11" t="inlineStr"/>
@@ -9378,22 +9388,22 @@
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C122" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E122" s="15" t="n">
@@ -9401,44 +9411,36 @@
       </c>
       <c r="F122" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G122" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H122" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J122" s="15" t="n">
         <v>22</v>
       </c>
       <c r="K122" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M122" s="15" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L122" s="15" t="inlineStr"/>
+      <c r="M122" s="15" t="inlineStr"/>
       <c r="N122" s="16" t="n">
-        <v>240</v>
-      </c>
-      <c r="O122" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P122" s="16" t="n">
@@ -9448,22 +9450,22 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -9471,7 +9473,7 @@
       </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G123" s="11" t="inlineStr">
@@ -9481,12 +9483,12 @@
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
@@ -9497,16 +9499,16 @@
       </c>
       <c r="L123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M123" s="11" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N123" s="12" t="n">
-        <v>557.145</v>
+        <v>240</v>
       </c>
       <c r="O123" s="13" t="n">
         <v>0</v>
@@ -9518,22 +9520,22 @@
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C124" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E124" s="15" t="n">
@@ -9546,7 +9548,7 @@
       </c>
       <c r="G124" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H124" s="15" t="inlineStr">
@@ -9556,21 +9558,29 @@
       </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J124" s="15" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K124" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L124" s="15" t="inlineStr"/>
-      <c r="M124" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L124" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M124" s="15" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N124" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O124" s="16" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O124" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P124" s="16" t="n">
@@ -9580,22 +9590,22 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
@@ -9618,14 +9628,14 @@
       </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="L125" s="11" t="inlineStr"/>
       <c r="M125" s="11" t="inlineStr"/>
@@ -9642,12 +9652,12 @@
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
@@ -9657,7 +9667,7 @@
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E126" s="15" t="n">
@@ -9675,19 +9685,19 @@
       </c>
       <c r="H126" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I126" s="15" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J126" s="15" t="n">
         <v>35</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="L126" s="15" t="inlineStr"/>
       <c r="M126" s="15" t="inlineStr"/>
@@ -9704,22 +9714,22 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -9735,17 +9745,21 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H127" s="11" t="inlineStr"/>
+      <c r="H127" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L127" s="11" t="inlineStr"/>
       <c r="M127" s="11" t="inlineStr"/>
@@ -9762,12 +9776,12 @@
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr">
@@ -9777,7 +9791,7 @@
       </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E128" s="15" t="n">
@@ -9793,32 +9807,20 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H128" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H128" s="15" t="inlineStr"/>
       <c r="I128" s="15" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J128" s="15" t="n">
         <v>37</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="L128" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M128" s="15" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L128" s="15" t="inlineStr"/>
+      <c r="M128" s="15" t="inlineStr"/>
       <c r="N128" s="16" t="n">
         <v>0</v>
       </c>
@@ -9832,22 +9834,22 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -9860,29 +9862,33 @@
       </c>
       <c r="G129" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H129" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H129" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J129" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>0.75</v>
+        <v>5.75</v>
       </c>
       <c r="L129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-25456</t>
+          <t>PDMDEP-34532</t>
         </is>
       </c>
       <c r="M129" s="11" t="inlineStr">
         <is>
-          <t>424152</t>
+          <t>412263</t>
         </is>
       </c>
       <c r="N129" s="12" t="n">
@@ -9898,24 +9904,26 @@
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12292</t>
         </is>
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C130" s="15" t="inlineStr"/>
+          <t>[CD06] Littéralis expert</t>
+        </is>
+      </c>
+      <c r="C130" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E130" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+        </is>
+      </c>
+      <c r="E130" s="15" t="n">
+        <v/>
       </c>
       <c r="F130" s="15" t="inlineStr">
         <is>
@@ -9924,17 +9932,13 @@
       </c>
       <c r="G130" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H130" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H130" s="15" t="inlineStr"/>
       <c r="I130" s="15" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J130" s="15" t="n">
@@ -9943,8 +9947,16 @@
       <c r="K130" s="15" t="n">
         <v>0.75</v>
       </c>
-      <c r="L130" s="15" t="inlineStr"/>
-      <c r="M130" s="15" t="inlineStr"/>
+      <c r="L130" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-25456</t>
+        </is>
+      </c>
+      <c r="M130" s="15" t="inlineStr">
+        <is>
+          <t>424152</t>
+        </is>
+      </c>
       <c r="N130" s="16" t="n">
         <v>0</v>
       </c>
@@ -9958,21 +9970,25 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>PSC-1363</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr"/>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
-        </is>
-      </c>
-      <c r="E131" s="11" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F131" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -9980,20 +9996,24 @@
       </c>
       <c r="G131" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H131" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H131" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I131" s="11" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J131" s="11" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="K131" s="11" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L131" s="11" t="inlineStr"/>
       <c r="M131" s="11" t="inlineStr"/>
@@ -10010,18 +10030,18 @@
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>PSC-1351</t>
+          <t>PSC-1363</t>
         </is>
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>MAIRIE DE CADENET</t>
         </is>
       </c>
       <c r="C132" s="15" t="inlineStr"/>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>MAIRIE DE CADENET</t>
         </is>
       </c>
       <c r="E132" s="15" t="inlineStr"/>
@@ -10038,11 +10058,11 @@
       <c r="H132" s="15" t="inlineStr"/>
       <c r="I132" s="15" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="J132" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K132" s="15" t="n">
         <v>0.25</v>
@@ -10062,18 +10082,18 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>PSC-1346</t>
+          <t>PSC-1351</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr"/>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr"/>
@@ -10090,7 +10110,7 @@
       <c r="H133" s="11" t="inlineStr"/>
       <c r="I133" s="11" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="J133" s="11" t="n">
@@ -10114,18 +10134,18 @@
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PSC-1346</t>
         </is>
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="C134" s="15" t="inlineStr"/>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="E134" s="15" t="inlineStr"/>
@@ -10136,35 +10156,27 @@
       </c>
       <c r="G134" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H134" s="15" t="inlineStr"/>
       <c r="I134" s="15" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="J134" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K134" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L134" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
-      <c r="M134" s="15" t="inlineStr">
-        <is>
-          <t>00177354</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L134" s="15" t="inlineStr"/>
+      <c r="M134" s="15" t="inlineStr"/>
       <c r="N134" s="16" t="n">
-        <v>450</v>
-      </c>
-      <c r="O134" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P134" s="16" t="n">
@@ -10174,18 +10186,18 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr"/>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr"/>
@@ -10196,27 +10208,35 @@
       </c>
       <c r="G135" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H135" s="11" t="inlineStr"/>
       <c r="I135" s="11" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J135" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L135" s="11" t="inlineStr"/>
-      <c r="M135" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L135" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M135" s="11" t="inlineStr">
+        <is>
+          <t>00177354</t>
+        </is>
+      </c>
       <c r="N135" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O135" s="12" t="n">
+        <v>450</v>
+      </c>
+      <c r="O135" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P135" s="12" t="n">
@@ -10226,18 +10246,18 @@
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C136" s="15" t="inlineStr"/>
       <c r="D136" s="15" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E136" s="15" t="inlineStr"/>
@@ -10254,14 +10274,14 @@
       <c r="H136" s="15" t="inlineStr"/>
       <c r="I136" s="15" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J136" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K136" s="15" t="n">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="L136" s="15" t="inlineStr"/>
       <c r="M136" s="15" t="inlineStr"/>
@@ -10278,18 +10298,18 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr"/>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E137" s="11" t="inlineStr"/>
@@ -10300,31 +10320,23 @@
       </c>
       <c r="G137" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H137" s="11" t="inlineStr"/>
       <c r="I137" s="11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J137" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K137" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L137" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M137" s="11" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="L137" s="11" t="inlineStr"/>
+      <c r="M137" s="11" t="inlineStr"/>
       <c r="N137" s="12" t="n">
         <v>0</v>
       </c>
@@ -10338,18 +10350,18 @@
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>PSC-1047</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C138" s="15" t="inlineStr"/>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E138" s="15" t="inlineStr"/>
@@ -10366,61 +10378,121 @@
       <c r="H138" s="15" t="inlineStr"/>
       <c r="I138" s="15" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J138" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K138" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L138" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M138" s="15" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N138" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1047</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr"/>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E139" s="11" t="inlineStr"/>
+      <c r="F139" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G139" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H139" s="11" t="inlineStr"/>
+      <c r="I139" s="11" t="inlineStr">
+        <is>
           <t>04/11/2025</t>
         </is>
       </c>
-      <c r="J138" s="15" t="n">
+      <c r="J139" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="K138" s="15" t="n">
+      <c r="K139" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L138" s="15" t="inlineStr">
+      <c r="L139" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-26768</t>
         </is>
       </c>
-      <c r="M138" s="15" t="inlineStr">
+      <c r="M139" s="11" t="inlineStr">
         <is>
           <t>00141775</t>
         </is>
       </c>
-      <c r="N138" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O138" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P138" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="17" t="inlineStr">
+      <c r="N139" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B139" s="17" t="inlineStr"/>
-      <c r="C139" s="17" t="inlineStr"/>
-      <c r="D139" s="17" t="inlineStr"/>
-      <c r="E139" s="17" t="inlineStr"/>
-      <c r="F139" s="17" t="inlineStr"/>
-      <c r="G139" s="17" t="inlineStr"/>
-      <c r="H139" s="17" t="inlineStr"/>
-      <c r="I139" s="17" t="inlineStr"/>
-      <c r="J139" s="17" t="inlineStr"/>
-      <c r="K139" s="17" t="inlineStr"/>
-      <c r="L139" s="17" t="inlineStr"/>
-      <c r="M139" s="17" t="inlineStr"/>
-      <c r="N139" s="18" t="n">
+      <c r="B140" s="17" t="inlineStr"/>
+      <c r="C140" s="17" t="inlineStr"/>
+      <c r="D140" s="17" t="inlineStr"/>
+      <c r="E140" s="17" t="inlineStr"/>
+      <c r="F140" s="17" t="inlineStr"/>
+      <c r="G140" s="17" t="inlineStr"/>
+      <c r="H140" s="17" t="inlineStr"/>
+      <c r="I140" s="17" t="inlineStr"/>
+      <c r="J140" s="17" t="inlineStr"/>
+      <c r="K140" s="17" t="inlineStr"/>
+      <c r="L140" s="17" t="inlineStr"/>
+      <c r="M140" s="17" t="inlineStr"/>
+      <c r="N140" s="18" t="n">
         <v>121514.862</v>
       </c>
-      <c r="O139" s="18" t="n">
+      <c r="O140" s="18" t="n">
         <v>3355.2</v>
       </c>
-      <c r="P139" s="18" t="n">
-        <v>34.92</v>
+      <c r="P140" s="18" t="n">
+        <v>33.11</v>
       </c>
     </row>
   </sheetData>
@@ -10560,6 +10632,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId133"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId135"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11371,26 +11444,26 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>59</v>
+        <v>63.5</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>11.75</v>
+        <v>12.5</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>3.33</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>74.08</v>
+        <v>79.33</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>7.75</v>
+        <v>8.25</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>508.2</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>15.6%</t>
         </is>
       </c>
     </row>

--- a/jira_export_2026-10-09.xlsx
+++ b/jira_export_2026-10-09.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>148 h</t>
+          <t>156 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -886,7 +886,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="N30" s="16" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="O30" s="16" t="n">
         <v>516</v>
@@ -4165,7 +4165,7 @@
         <v>4</v>
       </c>
       <c r="K48" s="15" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="L48" s="15" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>4</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>10</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>11</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>11</v>
       </c>
       <c r="K102" s="15" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>11</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>11</v>
       </c>
       <c r="K104" s="15" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>11</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>37</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="L129" s="11" t="inlineStr">
         <is>
@@ -10486,13 +10486,13 @@
       <c r="L140" s="17" t="inlineStr"/>
       <c r="M140" s="17" t="inlineStr"/>
       <c r="N140" s="18" t="n">
-        <v>121514.862</v>
+        <v>121729.862</v>
       </c>
       <c r="O140" s="18" t="n">
         <v>3355.2</v>
       </c>
       <c r="P140" s="18" t="n">
-        <v>33.11</v>
+        <v>31.48</v>
       </c>
     </row>
   </sheetData>
@@ -11444,16 +11444,16 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>63.5</v>
+        <v>68.25</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>3.33</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>79.33</v>
+        <v>84.58</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>8.25</v>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>16.6%</t>
         </is>
       </c>
     </row>
@@ -11505,7 +11505,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>37.33</v>
+        <v>39.58</v>
       </c>
     </row>
   </sheetData>
@@ -11669,7 +11669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11693,7 +11693,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 13 commande(s)</t>
+          <t>Épics créées ce mois — 14 commande(s)</t>
         </is>
       </c>
     </row>
@@ -11748,22 +11748,22 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-36236</t>
+          <t>PDMDEP-36335</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-36230</t>
+          <t>PDMDEP-36327</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIBERON</t>
+          <t>VILLE D'AIGLE</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>00183980</t>
+          <t>00184406</t>
         </is>
       </c>
       <c r="I5" s="25" t="n">
@@ -11793,12 +11793,12 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36214</t>
+          <t>PDMDEP-36236</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36205</t>
+          <t>PDMDEP-36230</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -11808,7 +11808,7 @@
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>COMME DE FECAMP</t>
+          <t>COMMUNE DE QUIBERON</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -11818,7 +11818,7 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -11828,7 +11828,7 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>00176659</t>
+          <t>00183980</t>
         </is>
       </c>
       <c r="I6" s="26" t="n">
@@ -11838,22 +11838,22 @@
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-36181</t>
+          <t>PDMDEP-36214</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-36174</t>
+          <t>PDMDEP-36205</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE AURAY</t>
+          <t>COMME DE FECAMP</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -11873,42 +11873,42 @@
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>00183814</t>
+          <t>00176659</t>
         </is>
       </c>
       <c r="I7" s="25" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36259</t>
+          <t>PDMDEP-36181</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36247</t>
+          <t>PDMDEP-36174</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D AVIGNON</t>
+          <t>COMMUNE DE AURAY</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -11916,15 +11916,19 @@
           <t>Services</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr"/>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>00183814</t>
+        </is>
+      </c>
       <c r="I8" s="26" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-36258</t>
+          <t>PDMDEP-36259</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
@@ -11957,11 +11961,7 @@
           <t>Services</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr">
-        <is>
-          <t>https:</t>
-        </is>
-      </c>
+      <c r="H9" s="15" t="inlineStr"/>
       <c r="I9" s="25" t="n">
         <v>0</v>
       </c>
@@ -11969,7 +11969,7 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36257</t>
+          <t>PDMDEP-36258</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>infos</t>
+          <t>https:</t>
         </is>
       </c>
       <c r="I10" s="26" t="n">
@@ -12014,7 +12014,7 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-36256</t>
+          <t>PDMDEP-36257</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
@@ -12049,7 +12049,7 @@
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>infos</t>
         </is>
       </c>
       <c r="I11" s="25" t="n">
@@ -12059,7 +12059,7 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36255</t>
+          <t>PDMDEP-36256</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>sogetask</t>
+          <t>#</t>
         </is>
       </c>
       <c r="I12" s="26" t="n">
@@ -12104,7 +12104,7 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-36254</t>
+          <t>PDMDEP-36255</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>1849345</t>
+          <t>sogetask</t>
         </is>
       </c>
       <c r="I13" s="25" t="n">
@@ -12149,7 +12149,7 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36253</t>
+          <t>PDMDEP-36254</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>apps.sogelink.fr</t>
+          <t>1849345</t>
         </is>
       </c>
       <c r="I14" s="26" t="n">
@@ -12194,7 +12194,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-36252</t>
+          <t>PDMDEP-36253</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
-          <t>tasks</t>
+          <t>apps.sogelink.fr</t>
         </is>
       </c>
       <c r="I15" s="25" t="n">
@@ -12239,22 +12239,22 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36197</t>
+          <t>PDMDEP-36252</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36190</t>
+          <t>PDMDEP-36247</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BAUGE-EN-ANJOU</t>
+          <t>COMMUNE D AVIGNON</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -12274,83 +12274,107 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>00183894</t>
+          <t>tasks</t>
         </is>
       </c>
       <c r="I16" s="26" t="n">
-        <v>5718</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
+          <t>PDMDEP-36197</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-36190</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE BAUGE-EN-ANJOU</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>00183894</t>
+        </is>
+      </c>
+      <c r="I17" s="25" t="n">
+        <v>5718</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
           <t>PDMDEP-36148</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-36144</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>VILLE DE VILLEFRANCHE SUR SAONE</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G17" s="15" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H17" s="15" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>00183228</t>
         </is>
       </c>
-      <c r="I17" s="25" t="n">
+      <c r="I18" s="26" t="n">
         <v>2310</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="17" t="n"/>
-      <c r="D18" s="17" t="n"/>
-      <c r="E18" s="17" t="n"/>
-      <c r="F18" s="17" t="n"/>
-      <c r="G18" s="17" t="n"/>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>13 commande(s)</t>
-        </is>
-      </c>
-      <c r="I18" s="24" t="n">
-        <v>9828</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B19" s="17" t="n"/>
@@ -12361,17 +12385,17 @@
       <c r="G19" s="17" t="n"/>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>10 commande(s)</t>
+          <t>14 commande(s)</t>
         </is>
       </c>
       <c r="I19" s="24" t="n">
-        <v>8028</v>
+        <v>9828</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B20" s="17" t="n"/>
@@ -12382,10 +12406,31 @@
       <c r="G20" s="17" t="n"/>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>3 commande(s)</t>
+          <t>10 commande(s)</t>
         </is>
       </c>
       <c r="I20" s="24" t="n">
+        <v>8028</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
+      <c r="G21" s="17" t="n"/>
+      <c r="H21" s="17" t="inlineStr">
+        <is>
+          <t>4 commande(s)</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="n">
         <v>1800</v>
       </c>
     </row>
@@ -12400,7 +12445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -12421,7 +12466,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>4 clôture(s) : 4 projet(s), 0 rework</t>
+          <t>5 clôture(s) : 5 projet(s), 0 rework</t>
         </is>
       </c>
     </row>
@@ -12578,32 +12623,62 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-35261</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>[VILLE DE VILLEURBANNE] - Reprise des données TLPE</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>VILLE DE VILLEURBANNE</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n"/>
-      <c r="C10" s="17" t="n"/>
-      <c r="D10" s="17" t="n"/>
-      <c r="E10" s="17" t="n"/>
-      <c r="F10" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B11" s="27" t="n"/>
-      <c r="C11" s="27" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="27" t="n"/>
-      <c r="F11" s="27" t="n">
+      <c r="B12" s="27" t="n"/>
+      <c r="C12" s="27" t="n"/>
+      <c r="D12" s="27" t="n"/>
+      <c r="E12" s="27" t="n"/>
+      <c r="F12" s="27" t="n">
         <v>0</v>
       </c>
     </row>
